--- a/data/out/variants/v8_only_gen_no_solar_enso/summary_v8_only_gen_no_solar_enso.xlsx
+++ b/data/out/variants/v8_only_gen_no_solar_enso/summary_v8_only_gen_no_solar_enso.xlsx
@@ -547,7 +547,7 @@
         <v>9639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03200030326843262</v>
+        <v>0.03394269943237305</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         <v>9639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02819967269897461</v>
+        <v>0.03071808815002441</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>9639</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08480167388916016</v>
+        <v>0.06526899337768555</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>9639</v>
       </c>
       <c r="M5" t="n">
-        <v>2.225594043731689</v>
+        <v>1.835608005523682</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>9639</v>
       </c>
       <c r="M6" t="n">
-        <v>5.002528190612793</v>
+        <v>6.058215379714966</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>9639</v>
       </c>
       <c r="M7" t="n">
-        <v>759.9858295917511</v>
+        <v>734.8105146884918</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>9639</v>
       </c>
       <c r="M8" t="n">
-        <v>391.5440616607666</v>
+        <v>369.70108294487</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>9639</v>
       </c>
       <c r="M9" t="n">
-        <v>235.7357556819916</v>
+        <v>225.6322894096375</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>9639</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9967958927154541</v>
+        <v>0.8934938907623291</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 903, 'learning_rate': 0.059247158656181104, 'max_depth': 4, 'subsample': 0.7311851503637755, 'colsample_bytree': 0.9977811507985296}</t>
+          <t>{'n_estimators': 757, 'learning_rate': 0.06809494071049664, 'max_depth': 5, 'subsample': 0.7365737141771324, 'colsample_bytree': 0.9113700239356376}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2525646077633206</v>
+        <v>0.219434758142634</v>
       </c>
       <c r="F11" t="n">
-        <v>240.2478355676987</v>
+        <v>246.0296944306468</v>
       </c>
       <c r="G11" t="n">
-        <v>187824.3582491346</v>
+        <v>196149.6166039401</v>
       </c>
       <c r="H11" t="n">
-        <v>433.387076698342</v>
+        <v>442.8878149192413</v>
       </c>
       <c r="I11" t="n">
-        <v>48.05544123796405</v>
+        <v>48.24334771845614</v>
       </c>
       <c r="J11" t="n">
         <v>48192</v>
@@ -1046,7 +1046,7 @@
         <v>9639</v>
       </c>
       <c r="M11" t="n">
-        <v>123.7799429893494</v>
+        <v>90.31645011901855</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 912, 'learning_rate': 0.014613519496790099, 'num_leaves': 89, 'min_child_samples': 50}</t>
+          <t>{'n_estimators': 224, 'learning_rate': 0.04109367512285426, 'num_leaves': 72, 'min_child_samples': 45}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1675008233397121</v>
+        <v>0.175030869941316</v>
       </c>
       <c r="F12" t="n">
-        <v>250.1057439608762</v>
+        <v>249.920670137095</v>
       </c>
       <c r="G12" t="n">
-        <v>209200.1866960537</v>
+        <v>207307.9480019507</v>
       </c>
       <c r="H12" t="n">
-        <v>457.3840691323363</v>
+        <v>455.310825702564</v>
       </c>
       <c r="I12" t="n">
-        <v>48.78171395984288</v>
+        <v>49.49135281528494</v>
       </c>
       <c r="J12" t="n">
         <v>48192</v>
@@ -1101,7 +1101,7 @@
         <v>9639</v>
       </c>
       <c r="M12" t="n">
-        <v>407.3272261619568</v>
+        <v>269.4547777175903</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 922, 'learning_rate': 0.043093437746625385, 'depth': 4}</t>
+          <t>{'iterations': 972, 'learning_rate': 0.09905701471517304, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.184490975524392</v>
+        <v>0.1954520778331668</v>
       </c>
       <c r="F13" t="n">
-        <v>251.4034646207414</v>
+        <v>247.4295995443967</v>
       </c>
       <c r="G13" t="n">
-        <v>204930.7013816198</v>
+        <v>202176.2666462136</v>
       </c>
       <c r="H13" t="n">
-        <v>452.6927229165716</v>
+        <v>449.6401523954612</v>
       </c>
       <c r="I13" t="n">
-        <v>48.43442329497847</v>
+        <v>47.45344130642313</v>
       </c>
       <c r="J13" t="n">
         <v>48192</v>
@@ -1156,7 +1156,7 @@
         <v>9639</v>
       </c>
       <c r="M13" t="n">
-        <v>303.1784098148346</v>
+        <v>279.8813517093658</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>9639</v>
       </c>
       <c r="M14" t="n">
-        <v>118.0515587329865</v>
+        <v>115.0541868209839</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>9639</v>
       </c>
       <c r="M15" t="n">
-        <v>26.19902896881104</v>
+        <v>27.62657165527344</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>9639</v>
       </c>
       <c r="M16" t="n">
-        <v>692.3503370285034</v>
+        <v>1513.882669448853</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
